--- a/whitelist_matriculas.xlsx
+++ b/whitelist_matriculas.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.monaco\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedro.monaco\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD40555A-E3E2-41F5-8AA9-788CB32D3D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9335ECB-1CC1-409C-80F6-7B641160148D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="638">
   <si>
     <t>matricula</t>
   </si>
@@ -101,9 +101,6 @@
     <t>ELIAS APOLINARIO</t>
   </si>
   <si>
-    <t>WILLIAN RIBEIRO DA SILVA</t>
-  </si>
-  <si>
     <t>CAIO VINICIUS BRAGATTO PEREIRA</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>CARLOS GONCALVES DA SILVA</t>
   </si>
   <si>
-    <t>WALLACE FABRICIO MEDEIROS</t>
-  </si>
-  <si>
     <t>LYNDOMAR DIOGO DE OLIVEIRA</t>
   </si>
   <si>
@@ -287,12 +281,6 @@
     <t>WALLACE FERNANDO DE SOUZA BENTO</t>
   </si>
   <si>
-    <t>RAILTON FELIX SANTOS</t>
-  </si>
-  <si>
-    <t>MACKSON DA SILVA RIBEIRO</t>
-  </si>
-  <si>
     <t>CARLOS WAGNER DOS REIS SANTOS</t>
   </si>
   <si>
@@ -350,9 +338,6 @@
     <t>CELIO SILVA DE ASSIS</t>
   </si>
   <si>
-    <t>IGOR FERREIRA LINHARES</t>
-  </si>
-  <si>
     <t>FABIO RIBEIRO BATISTA</t>
   </si>
   <si>
@@ -386,15 +371,9 @@
     <t>EDMILSON PEREIRA DA SILVA</t>
   </si>
   <si>
-    <t>MAIQ RANGEL DE ASSIS</t>
-  </si>
-  <si>
     <t>DIEISON ROBERTO RODRIGUES DA SILVA</t>
   </si>
   <si>
-    <t>EDILSON PASCOAL DA HORA</t>
-  </si>
-  <si>
     <t>MARCELO ALVES DE PAULA</t>
   </si>
   <si>
@@ -464,9 +443,6 @@
     <t>DANIEL DE SOUZA CRUZ</t>
   </si>
   <si>
-    <t>LUAN CARNEIRO CIDRINI</t>
-  </si>
-  <si>
     <t>MARCELO CORDEIRO</t>
   </si>
   <si>
@@ -503,9 +479,6 @@
     <t>MARCOS ALVES FERREIRA</t>
   </si>
   <si>
-    <t>RICARDO BRAGA TEIXEIRA</t>
-  </si>
-  <si>
     <t xml:space="preserve">ADILSON SEBASTIÃO DE LIMA VARGAS </t>
   </si>
   <si>
@@ -536,18 +509,12 @@
     <t>WALNEI AMARO DA SILVA</t>
   </si>
   <si>
-    <t>RAFAEL GONÇALVES DA SILVA</t>
-  </si>
-  <si>
     <t>ROGERIO RIBEIRO DE CARVALHO</t>
   </si>
   <si>
     <t>CLEBIO BARROS DE MENEZES</t>
   </si>
   <si>
-    <t>CARLOS ANTONIO MORAIS DA SILVA</t>
-  </si>
-  <si>
     <t>KELLI MARCIA SANTOS DA SILVA</t>
   </si>
   <si>
@@ -626,9 +593,6 @@
     <t>HIDAILTON WERILIOVEIKERSON SILVA DE OLIVEIRA</t>
   </si>
   <si>
-    <t>EDEMILSON MARINHO DO NASCIMENTO</t>
-  </si>
-  <si>
     <t>JOSIAS CUSTODIO DE LIMA</t>
   </si>
   <si>
@@ -638,9 +602,6 @@
     <t>ADRIANO SILVA</t>
   </si>
   <si>
-    <t>HERLEI CEZAR DA SILVA CHAGAS</t>
-  </si>
-  <si>
     <t>WELLINGTON SILVA GONCALVES</t>
   </si>
   <si>
@@ -710,9 +671,6 @@
     <t>LUCIANO DA SILVA LOPES CALADO</t>
   </si>
   <si>
-    <t>WILLIAM RAMOS DOS SANTOS</t>
-  </si>
-  <si>
     <t>RAFAEL DOMINGUES DE SOUZA</t>
   </si>
   <si>
@@ -728,21 +686,12 @@
     <t>WALACE PEREIRA</t>
   </si>
   <si>
-    <t>THIAGO VIEIRA IGNACIO</t>
-  </si>
-  <si>
     <t>PAULO FERREIRA DOS SANTOS</t>
   </si>
   <si>
     <t>FILIPE DE PAULA AZEVEDO</t>
   </si>
   <si>
-    <t>LEONARDO DE ARAUJO MONTEIRO</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO SOARES FILHO</t>
-  </si>
-  <si>
     <t>ANDERSON DA SILVA</t>
   </si>
   <si>
@@ -827,9 +776,6 @@
     <t>MARCOS DA GUIA CARVALHO</t>
   </si>
   <si>
-    <t>VALDEMIR DOS SANTOS SILVA</t>
-  </si>
-  <si>
     <t>WELTON FERNANDES RIBEIRO</t>
   </si>
   <si>
@@ -845,18 +791,12 @@
     <t>WANDERSON REIS DE SOUSA</t>
   </si>
   <si>
-    <t>MARCELO DOS SANTOS SILVA</t>
-  </si>
-  <si>
     <t>ALEXANDRE DA SILVA CASTRO</t>
   </si>
   <si>
     <t>PAULO ROBERTO AMARAL DE SOUZA</t>
   </si>
   <si>
-    <t>FLAVIA MARIA DA SILVA</t>
-  </si>
-  <si>
     <t>MAIC CONCEICAO DA SILVA</t>
   </si>
   <si>
@@ -935,9 +875,6 @@
     <t>WESLLEY HENRIQUE PEREIRA SOARES</t>
   </si>
   <si>
-    <t>LEONARDO CARLOS MANGEA</t>
-  </si>
-  <si>
     <t>MARCOS EDUARDO DE SALES RAMOS</t>
   </si>
   <si>
@@ -968,9 +905,6 @@
     <t xml:space="preserve">JOÃO VITOR DA SILVA </t>
   </si>
   <si>
-    <t>DIEGO OLIVEIRA DE PAULA</t>
-  </si>
-  <si>
     <t>MARCIO AUGUSTO NEIVA JUNIOR</t>
   </si>
   <si>
@@ -986,15 +920,9 @@
     <t xml:space="preserve">DENISSON ROBERTO CHAGAS GONÇALVES </t>
   </si>
   <si>
-    <t>CAIQUE ANDRADE SILVA</t>
-  </si>
-  <si>
     <t>WALMIR PEREIRA PINHEIRO</t>
   </si>
   <si>
-    <t>JEFERSON BASILIO FARIAS</t>
-  </si>
-  <si>
     <t xml:space="preserve">RODOLFO AGUIAR DOS SANTOS </t>
   </si>
   <si>
@@ -1013,9 +941,6 @@
     <t>JUAN GONÇALVES MUNIZ</t>
   </si>
   <si>
-    <t xml:space="preserve">MARCOS GASPAR RIBEIRO DOS SANTOS </t>
-  </si>
-  <si>
     <t>JOACI DE CAMPOS CLEMENTE</t>
   </si>
   <si>
@@ -1049,12 +974,6 @@
     <t xml:space="preserve">LEANDRO DO CARMO CAMPOS </t>
   </si>
   <si>
-    <t>NATAN MAGALHÃES SILVA</t>
-  </si>
-  <si>
-    <t>THIAGO SILVA BARRETO</t>
-  </si>
-  <si>
     <t>JOAO BATISTA GULARTE</t>
   </si>
   <si>
@@ -1151,15 +1070,9 @@
     <t>MATEUS DA COSTA OVIDIO</t>
   </si>
   <si>
-    <t>VINICIUS RIBEIRO PINTO</t>
-  </si>
-  <si>
     <t xml:space="preserve">MARCIO RODRIGUES SE PULVEDA </t>
   </si>
   <si>
-    <t xml:space="preserve">JOSÉ EDUARDO PEREIRA DE OLIVEIRA </t>
-  </si>
-  <si>
     <t>THIAGO DA SILVA OLIVEIRA MOTTA</t>
   </si>
   <si>
@@ -1202,15 +1115,9 @@
     <t xml:space="preserve">RIVALDO HENRIQUE </t>
   </si>
   <si>
-    <t xml:space="preserve">VITOR VAZ DA SIVA </t>
-  </si>
-  <si>
     <t xml:space="preserve">MAGNO VENTURA SENRA </t>
   </si>
   <si>
-    <t xml:space="preserve">RONALDO DOS SANTOS </t>
-  </si>
-  <si>
     <t xml:space="preserve">JULIO CESAR PEREIRA DA SILVA </t>
   </si>
   <si>
@@ -1238,15 +1145,9 @@
     <t>PEDRO AUGUSTO SILVA DE FRANÇA</t>
   </si>
   <si>
-    <t xml:space="preserve">JOSIEL CORREA TEIXEIRA </t>
-  </si>
-  <si>
     <t xml:space="preserve">BENEDITO DA SILVA </t>
   </si>
   <si>
-    <t xml:space="preserve">FERNANDO SOUZA DA COSTA </t>
-  </si>
-  <si>
     <t xml:space="preserve">LUZIMAR SOUZA SANTOS </t>
   </si>
   <si>
@@ -1280,9 +1181,6 @@
     <t>ERASMO DOS SANTOS REIS</t>
   </si>
   <si>
-    <t xml:space="preserve">ADESIO FERREIRA LIMA </t>
-  </si>
-  <si>
     <t xml:space="preserve">ANTÔNIO CARLOS DA SILVA </t>
   </si>
   <si>
@@ -1292,30 +1190,18 @@
     <t>RICARDO DOS SANTOS COSTA</t>
   </si>
   <si>
-    <t>ACTHUS PHILLIPPE DE OLIVEIRA SILVA DINIZ</t>
-  </si>
-  <si>
     <t>CELSO LUIZ FERREIRA DE PAULA</t>
   </si>
   <si>
-    <t>CARLOS MIGUEL BERNARDO DOS SANTOS</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALOISIO DE FRANÇA ANDRADE </t>
   </si>
   <si>
     <t>ROGERIO SERAFIM DOS SANTOS</t>
   </si>
   <si>
-    <t>LEONARDO DOS SANTOS CORREA</t>
-  </si>
-  <si>
     <t>FELIPE OLIVEIRA DAS CHAGAS</t>
   </si>
   <si>
-    <t>LEONARDO DE OLIVEIRA SILVA</t>
-  </si>
-  <si>
     <t>LUCAS PEREIRA DE MELO</t>
   </si>
   <si>
@@ -1337,18 +1223,12 @@
     <t xml:space="preserve">ISAEL OLIVEIRA DE PAULA </t>
   </si>
   <si>
-    <t xml:space="preserve">CARLOS HENRIQUE SILVA JUNIOR </t>
-  </si>
-  <si>
     <t>VANDER NUNES VITORIA</t>
   </si>
   <si>
     <t xml:space="preserve">JUNIOR SANTOS DA SILVA </t>
   </si>
   <si>
-    <t xml:space="preserve">GLAUCIO SIQUEIRA SILVA </t>
-  </si>
-  <si>
     <t xml:space="preserve">RAIMUNDO VICENTE SOUZA </t>
   </si>
   <si>
@@ -1361,9 +1241,6 @@
     <t>ADEILSON ALMEIDA DE OLIVEIRA</t>
   </si>
   <si>
-    <t>JOAO PAULO MARTINS GUIMARAES</t>
-  </si>
-  <si>
     <t>ANDRE EMERICK RASTOPOLIS</t>
   </si>
   <si>
@@ -1427,9 +1304,6 @@
     <t>GUTEMBERG DOS SANTOS ALMEIDA FILHO</t>
   </si>
   <si>
-    <t>VAGNER RODRIGUES DA CONCEICAO</t>
-  </si>
-  <si>
     <t>PAULO ROBERTO DOS SANTOS CUNHA</t>
   </si>
   <si>
@@ -1451,12 +1325,6 @@
     <t>VINICIUS AGUIAR DA SILVA</t>
   </si>
   <si>
-    <t>FABIANO RODRIGUES DE CARVALHO</t>
-  </si>
-  <si>
-    <t>ALESSANDRO ASSIS AZEVEDO</t>
-  </si>
-  <si>
     <t>INGRID LEAL DE SOUZA BARBOSA</t>
   </si>
   <si>
@@ -1472,15 +1340,6 @@
     <t>RONALDO VITOR QUINTINO</t>
   </si>
   <si>
-    <t xml:space="preserve">FLAVIO AZEVEDO QUEIROZ </t>
-  </si>
-  <si>
-    <t>FILIPE SOUZA DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>AMANDA FERREIRA</t>
-  </si>
-  <si>
     <t>MAICON VITERBO DE SOUZA</t>
   </si>
   <si>
@@ -1517,21 +1376,9 @@
     <t xml:space="preserve">ALEX DOS SANTOS SOUSA </t>
   </si>
   <si>
-    <t>SILVANA QUINTINO DE SOUZA TEIXEIRA</t>
-  </si>
-  <si>
     <t>ALEXANDRE BARRETO FERREIRA BENTO</t>
   </si>
   <si>
-    <t>SAULO MAURICIO GUIMARÃES DE CARVALHO LOUZADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRENNYER DE OLIVEIRA RODRIGUES </t>
-  </si>
-  <si>
-    <t>ALMIR PALAZZI DOS SANTOS JUNIOR</t>
-  </si>
-  <si>
     <t>DOUGLAS DA CONCIÇÃO LIMA</t>
   </si>
   <si>
@@ -1547,9 +1394,6 @@
     <t xml:space="preserve">ELBERTI JORGE DE OLIVEIRA </t>
   </si>
   <si>
-    <t>JEFFERSON LUIS DOS SANTOS PACHECO</t>
-  </si>
-  <si>
     <t>RAFAEL MARQUES RIBEIRO</t>
   </si>
   <si>
@@ -1562,9 +1406,6 @@
     <t xml:space="preserve">BRUNO FALCAO DOS SANTOS </t>
   </si>
   <si>
-    <t>FELIPE BRANDÃO LOURENÇO</t>
-  </si>
-  <si>
     <t>CAUE DE SOUZA PEDROSO DE MORAES</t>
   </si>
   <si>
@@ -1595,18 +1436,12 @@
     <t>RODRIGO DE FREITAS BESSA BRITO</t>
   </si>
   <si>
-    <t>DOUGLAS COUTINHO JURDINO</t>
-  </si>
-  <si>
     <t>ARAO LAURINDO PEREIRA</t>
   </si>
   <si>
     <t xml:space="preserve">THIAGO DA SILVA LIMA </t>
   </si>
   <si>
-    <t xml:space="preserve">FLAVIAN SOUSA DA SILVA </t>
-  </si>
-  <si>
     <t xml:space="preserve">JOSÉ MAIKLEYTON DA SILVA MARTINS </t>
   </si>
   <si>
@@ -1622,9 +1457,6 @@
     <t xml:space="preserve">ABEL CAMBOIM COUTINHO DOS SANTOS </t>
   </si>
   <si>
-    <t>DEIVID MAYKON ARAUJO PAIVA</t>
-  </si>
-  <si>
     <t>ANA PAULA GENARIA DE SOUZA</t>
   </si>
   <si>
@@ -1637,9 +1469,6 @@
     <t>ANDERSON EDUARDO DE CARVALHO MATHIAS</t>
   </si>
   <si>
-    <t>JOELCIO VITORINO DO NASCIMENTO</t>
-  </si>
-  <si>
     <t xml:space="preserve">KAIO SILVA DE OLIVEIRA </t>
   </si>
   <si>
@@ -1673,9 +1502,6 @@
     <t>ALEXANDER LUIZ DE SOUZA</t>
   </si>
   <si>
-    <t>ROGER CARMO DA GUIA</t>
-  </si>
-  <si>
     <t>YURI OLIVEIRA CERQUEIRA</t>
   </si>
   <si>
@@ -1709,9 +1535,6 @@
     <t>MARCUS VINICIUS CELLURA DOS SANTOS</t>
   </si>
   <si>
-    <t>VITOR PEREIRA DE OLIVEIRA</t>
-  </si>
-  <si>
     <t>CYNTHIA RAFAELE CARDOZO DE LIMA</t>
   </si>
   <si>
@@ -1733,9 +1556,6 @@
     <t>KLEBER DO NASCIMENTO CUNHA</t>
   </si>
   <si>
-    <t>ANDERSON COELHO DE AZEVEDO</t>
-  </si>
-  <si>
     <t>CELIO DA SILVA CRUZ JUNIOR</t>
   </si>
   <si>
@@ -1754,9 +1574,6 @@
     <t>ENIR MACEDO DINIZ</t>
   </si>
   <si>
-    <t>YELSON DA LUZ HENRIQUE</t>
-  </si>
-  <si>
     <t>FRANCISCO EDIGLE DA SILVA</t>
   </si>
   <si>
@@ -1784,9 +1601,6 @@
     <t>ANDERSON LEITE MORAES</t>
   </si>
   <si>
-    <t>CARLOS ALBERTO RIBEIRO LIMA</t>
-  </si>
-  <si>
     <t>FABIANO FERREIRA DA SILVA</t>
   </si>
   <si>
@@ -1796,18 +1610,12 @@
     <t xml:space="preserve">ANTONY DO NASCIMENTO VERGILIO </t>
   </si>
   <si>
-    <t xml:space="preserve">DOUGLAS GOMES DE OLIVEIRA </t>
-  </si>
-  <si>
     <t>ELISEU SIMÕES DA CRUZ</t>
   </si>
   <si>
     <t>ROSILEY DOS SANTOS OZORIO FILHO</t>
   </si>
   <si>
-    <t>GLEYDSON JAYME DA ROSA</t>
-  </si>
-  <si>
     <t>WAGNER FARIS COUTO</t>
   </si>
   <si>
@@ -1817,36 +1625,24 @@
     <t xml:space="preserve">JOÃO VICTOR DA SILVA SOUZA </t>
   </si>
   <si>
-    <t xml:space="preserve">IGOR GOUVEIA DE SOUSA </t>
-  </si>
-  <si>
     <t>RODRIGO ALMEIDA DA SILVA</t>
   </si>
   <si>
     <t>ULISSES DE MEDEIROS CAMARGO</t>
   </si>
   <si>
-    <t>GUILHERME MONTEIRO DA CUNHA ARAUJO</t>
-  </si>
-  <si>
     <t>LUIZ FELIPE SOARES DO NASCIMENTO</t>
   </si>
   <si>
     <t xml:space="preserve">ADRIANO AMARO DE SOUSA </t>
   </si>
   <si>
-    <t>BRUNO PIMENTEL DA SILVA</t>
-  </si>
-  <si>
     <t xml:space="preserve">LENNON DE ARAÚJO RAIMUNDO </t>
   </si>
   <si>
     <t>MICHAEL VINICIUS PAULINO DA CRUZ</t>
   </si>
   <si>
-    <t>KEVYN MAYROU LEONE AMORIM DA CUNHA</t>
-  </si>
-  <si>
     <t>GILIARDE PIMENTA RAMOS</t>
   </si>
   <si>
@@ -1859,15 +1655,6 @@
     <t xml:space="preserve">MATHEUS DA SILVA BARBOSA </t>
   </si>
   <si>
-    <t>ANTÔNIO SILVA DE ARÚJO</t>
-  </si>
-  <si>
-    <t>UESLER DA SILVA MEDEIROS</t>
-  </si>
-  <si>
-    <t>FELIPE RODRIGUES DE ANDRADE</t>
-  </si>
-  <si>
     <t>FELIPE DA CONCEICAO AZEVEDO</t>
   </si>
   <si>
@@ -1886,9 +1673,6 @@
     <t>ANDERSON DE SOUZA</t>
   </si>
   <si>
-    <t xml:space="preserve">CARLOS EDUARDO ARAUJO FERREIRA </t>
-  </si>
-  <si>
     <t xml:space="preserve">ANDRE LUIS CORDEIRO DE SOUZA </t>
   </si>
   <si>
@@ -1898,9 +1682,6 @@
     <t>FLAVIO RODRIGUES TAVARES</t>
   </si>
   <si>
-    <t>EDIVANIO SILVEIRA DE PAIVA</t>
-  </si>
-  <si>
     <t>ALAN DA SILVA LOIOLA</t>
   </si>
   <si>
@@ -1934,9 +1715,6 @@
     <t>WELLINGTON OLIVEIRA FERREIRA</t>
   </si>
   <si>
-    <t>AILLON LUCAS DA SILVA MAGNO</t>
-  </si>
-  <si>
     <t xml:space="preserve">MOACIR JUNIO DANTAS DA SILVA </t>
   </si>
   <si>
@@ -1976,9 +1754,6 @@
     <t>JOAO FERREIRA CARVALHO</t>
   </si>
   <si>
-    <t>RAFAEL SOUZA DA SILVA</t>
-  </si>
-  <si>
     <t>ANDERSON ALMEIDA DE LIMA</t>
   </si>
   <si>
@@ -1997,9 +1772,6 @@
     <t>DAVID LEITE BORGES</t>
   </si>
   <si>
-    <t>ADEMARIO MARQUES MAGNO</t>
-  </si>
-  <si>
     <t>EVERTON FERREIRA DO NASCIMENTO</t>
   </si>
   <si>
@@ -2054,9 +1826,6 @@
     <t>Assistente Técnico</t>
   </si>
   <si>
-    <t>Encarregado de Montagem</t>
-  </si>
-  <si>
     <t>Gerente de Acabamento</t>
   </si>
   <si>
@@ -2120,9 +1889,6 @@
     <t> Esmerilhador</t>
   </si>
   <si>
-    <t>Assistente Técnico I</t>
-  </si>
-  <si>
     <t xml:space="preserve">Supervisor de Produção </t>
   </si>
   <si>
@@ -2157,6 +1923,33 @@
   </si>
   <si>
     <t>Auxiliar de Planejamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Líder de montagem </t>
+  </si>
+  <si>
+    <t>Auxiliar de Planejamento I</t>
+  </si>
+  <si>
+    <t>ROSILAINE HELENA QUIRINO HENRIQUES</t>
+  </si>
+  <si>
+    <t>JHONY FERREIRA PASTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUGLAS DA SILVA TEIXEIRA </t>
+  </si>
+  <si>
+    <t>ANDRE FELIPE MOREIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JORGE CONCEIÇÃO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSIMARA DA SILVA SANTOS </t>
+  </si>
+  <si>
+    <t>Engenheira Treinee</t>
   </si>
 </sst>
 </file>
@@ -2231,12 +2024,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3945140-4D1D-4931-9077-ACAB0AE9BAFF}" name="Tabela1" displayName="Tabela1" ref="A1:C659" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:C659" xr:uid="{C3945140-4D1D-4931-9077-ACAB0AE9BAFF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3945140-4D1D-4931-9077-ACAB0AE9BAFF}" name="Tabela1" displayName="Tabela1" ref="A1:C589" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+  <autoFilter ref="A1:C589" xr:uid="{C3945140-4D1D-4931-9077-ACAB0AE9BAFF}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{54C91657-2FFB-4A38-9B69-39564DE5B4FC}" name="matricula" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{1562F139-FD7A-4D20-B0A6-A75CFEB4FD90}" name="nome" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{50E518E1-28EE-425A-8802-FC7321A09F0D}" name="funcao" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{54C91657-2FFB-4A38-9B69-39564DE5B4FC}" name="matricula" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{1562F139-FD7A-4D20-B0A6-A75CFEB4FD90}" name="nome" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{50E518E1-28EE-425A-8802-FC7321A09F0D}" name="funcao" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2505,7 +2298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C659"/>
+  <dimension ref="A1:C589"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1" customWidth="1"/>
@@ -2532,7 +2325,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>661</v>
+        <v>585</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2543,7 +2336,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>662</v>
+        <v>586</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2554,7 +2347,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>661</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2565,7 +2358,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>663</v>
+        <v>587</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2576,7 +2369,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>664</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2587,7 +2380,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>665</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2598,7 +2391,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>666</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2609,7 +2402,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>664</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2620,7 +2413,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>667</v>
+        <v>591</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2631,7 +2424,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>668</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2642,7 +2435,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>669</v>
+        <v>593</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2653,7 +2446,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>670</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2664,7 +2457,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>664</v>
+        <v>588</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2675,7 +2468,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>671</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2686,7 +2479,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>664</v>
+        <v>588</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2697,7 +2490,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>664</v>
+        <v>588</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2708,7 +2501,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>667</v>
+        <v>591</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2719,7047 +2512,6277 @@
         <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>661</v>
+        <v>585</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>20920</v>
+        <v>21579</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>672</v>
+        <v>596</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>21579</v>
+        <v>25848</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>673</v>
+        <v>597</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>25848</v>
+        <v>25900</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>674</v>
+        <v>590</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>25900</v>
+        <v>27469</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>666</v>
+        <v>598</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>27469</v>
+        <v>29762</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>675</v>
+        <v>599</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>29762</v>
+        <v>29780</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>29780</v>
+        <v>29781</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>29781</v>
+        <v>29829</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>677</v>
+        <v>595</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>29829</v>
+        <v>29849</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>671</v>
+        <v>601</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>29849</v>
+        <v>29850</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>678</v>
+        <v>590</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>29850</v>
+        <v>29915</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>666</v>
+        <v>602</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>29915</v>
+        <v>29916</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>679</v>
+        <v>603</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>29916</v>
+        <v>29922</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>680</v>
+        <v>591</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>29917</v>
+        <v>30071</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>29922</v>
+        <v>30075</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>667</v>
+        <v>604</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>30071</v>
+        <v>30079</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>30075</v>
+        <v>30885</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>37</v>
+        <v>386</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>681</v>
+        <v>590</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>30079</v>
+        <v>30886</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>677</v>
+        <v>599</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>33470</v>
+        <v>30888</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>671</v>
+        <v>600</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>30886</v>
+        <v>30890</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>676</v>
+        <v>605</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>30888</v>
+        <v>30891</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>30890</v>
+        <v>30892</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>682</v>
+        <v>606</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>30891</v>
+        <v>30896</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>675</v>
+        <v>590</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>30892</v>
+        <v>30902</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>683</v>
+        <v>605</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>30896</v>
+        <v>30906</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>666</v>
+        <v>598</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>30902</v>
+        <v>30907</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>682</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>30906</v>
+        <v>30910</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>675</v>
+        <v>591</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>30907</v>
+        <v>30916</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>677</v>
+        <v>591</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>30910</v>
+        <v>30926</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>667</v>
+        <v>600</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>30916</v>
+        <v>30928</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>667</v>
+        <v>590</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>30926</v>
+        <v>30929</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>30928</v>
+        <v>30931</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>677</v>
+        <v>629</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>30929</v>
+        <v>30932</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>677</v>
+        <v>588</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>30931</v>
+        <v>30934</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>30932</v>
+        <v>30957</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>664</v>
+        <v>607</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>30934</v>
+        <v>30961</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>30957</v>
+        <v>30963</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>57</v>
+        <v>460</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>684</v>
+        <v>598</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>30961</v>
+        <v>30964</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>677</v>
+        <v>602</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>30974</v>
+        <v>30965</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>30964</v>
+        <v>30966</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>679</v>
+        <v>598</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>30965</v>
+        <v>30967</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>682</v>
+        <v>591</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>30966</v>
+        <v>30968</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>675</v>
+        <v>590</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>30967</v>
+        <v>30974</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>667</v>
+        <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>30968</v>
+        <v>30996</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>666</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>32209</v>
+        <v>31035</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>30996</v>
+        <v>31040</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>31035</v>
+        <v>31041</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>675</v>
+        <v>602</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>31040</v>
+        <v>31042</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>675</v>
+        <v>602</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>31041</v>
+        <v>31044</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>679</v>
+        <v>605</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>31042</v>
+        <v>31053</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>679</v>
+        <v>630</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>31044</v>
+        <v>31061</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>675</v>
+        <v>591</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>31053</v>
+        <v>31278</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>72</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>678</v>
+        <v>590</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>31061</v>
+        <v>31279</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>667</v>
+        <v>608</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>31278</v>
+        <v>31282</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>666</v>
+        <v>590</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>31279</v>
+        <v>31284</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>685</v>
+        <v>609</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>31282</v>
+        <v>31287</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>685</v>
+        <v>610</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>31284</v>
+        <v>31289</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>77</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>686</v>
+        <v>610</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>31287</v>
+        <v>31290</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>78</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>687</v>
+        <v>610</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>31289</v>
+        <v>31292</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>687</v>
+        <v>611</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>31290</v>
+        <v>31295</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>687</v>
+        <v>590</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>31292</v>
+        <v>31335</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>81</v>
+        <v>424</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>688</v>
+        <v>599</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>31295</v>
+        <v>31351</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>666</v>
+        <v>599</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>32497</v>
+        <v>31365</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>31343</v>
+        <v>31389</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>663</v>
+        <v>587</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>31351</v>
+        <v>31394</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>31365</v>
+        <v>31413</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>682</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>31389</v>
+        <v>31428</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>663</v>
+        <v>587</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>31394</v>
+        <v>31439</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>31413</v>
+        <v>31441</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>31428</v>
+        <v>31496</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>663</v>
+        <v>600</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>31439</v>
+        <v>31497</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>677</v>
+        <v>590</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>31441</v>
+        <v>31499</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>31496</v>
+        <v>31502</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>31497</v>
+        <v>31506</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>31499</v>
+        <v>31555</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>31502</v>
+        <v>31580</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>677</v>
+        <v>590</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>31506</v>
+        <v>31582</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>31555</v>
+        <v>31583</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>31580</v>
+        <v>31589</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>31582</v>
+        <v>31590</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>31583</v>
+        <v>31617</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>675</v>
+        <v>605</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>31589</v>
+        <v>31621</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>675</v>
+        <v>599</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>31590</v>
+        <v>31639</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>675</v>
+        <v>609</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>31597</v>
+        <v>31650</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>31617</v>
+        <v>31688</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>682</v>
+        <v>598</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>31621</v>
+        <v>31690</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>676</v>
+        <v>612</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>31639</v>
+        <v>31693</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>686</v>
+        <v>612</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>31650</v>
+        <v>31713</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>31688</v>
+        <v>31721</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>31690</v>
+        <v>31723</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>31693</v>
+        <v>31738</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>689</v>
+        <v>613</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>31713</v>
+        <v>31810</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>31721</v>
+        <v>31821</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>31723</v>
+        <v>31836</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>677</v>
+        <v>614</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>31738</v>
+        <v>31856</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>690</v>
+        <v>612</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>31750</v>
+        <v>31896</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>677</v>
+        <v>602</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>31810</v>
+        <v>31931</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>682</v>
+        <v>598</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>31819</v>
+        <v>31935</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>675</v>
+        <v>585</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>31821</v>
+        <v>31950</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>675</v>
+        <v>601</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>31836</v>
+        <v>31960</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>691</v>
+        <v>612</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>31856</v>
+        <v>32035</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>31896</v>
+        <v>32042</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>679</v>
+        <v>598</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>31931</v>
+        <v>32055</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>123</v>
+        <v>504</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>31935</v>
+        <v>32081</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>661</v>
+        <v>598</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>31950</v>
+        <v>32085</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>678</v>
+        <v>602</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>31960</v>
+        <v>32127</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>32035</v>
+        <v>32155</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>32042</v>
+        <v>32188</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>32081</v>
+        <v>32192</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>32085</v>
+        <v>32209</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>679</v>
+        <v>600</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>32127</v>
+        <v>32211</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>677</v>
+        <v>588</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>32155</v>
+        <v>32339</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>677</v>
+        <v>591</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>32188</v>
+        <v>32448</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>677</v>
+        <v>585</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>32192</v>
+        <v>32457</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>38555</v>
+        <v>32464</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>677</v>
+        <v>590</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>32211</v>
+        <v>32495</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>664</v>
+        <v>600</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>32339</v>
+        <v>32540</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>667</v>
+        <v>600</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>32448</v>
+        <v>32778</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>661</v>
+        <v>600</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>32457</v>
+        <v>32789</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>677</v>
+        <v>590</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>32464</v>
+        <v>32792</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>32495</v>
+        <v>32793</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>41375</v>
+        <v>32798</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>32540</v>
+        <v>32848</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>677</v>
+        <v>604</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>32778</v>
+        <v>32850</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>32789</v>
+        <v>32852</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>32792</v>
+        <v>32856</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>32793</v>
+        <v>32858</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>32798</v>
+        <v>32866</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>32848</v>
+        <v>32930</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>681</v>
+        <v>585</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>32850</v>
+        <v>32971</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>32852</v>
+        <v>32988</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>32856</v>
+        <v>32998</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>32858</v>
+        <v>33005</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>677</v>
+        <v>590</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>32866</v>
+        <v>33014</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>677</v>
+        <v>590</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>32903</v>
+        <v>33025</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>687</v>
+        <v>590</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>32930</v>
+        <v>33098</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>661</v>
+        <v>612</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>32971</v>
+        <v>33100</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>32988</v>
+        <v>33105</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>32998</v>
+        <v>33127</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>33005</v>
+        <v>33130</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>666</v>
+        <v>605</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>33014</v>
+        <v>33154</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>33025</v>
+        <v>33193</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>33098</v>
+        <v>33199</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>689</v>
+        <v>611</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>33100</v>
+        <v>33201</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>33105</v>
+        <v>33221</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>41967</v>
+        <v>33242</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>33130</v>
+        <v>33263</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>675</v>
+        <v>605</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>33154</v>
+        <v>33337</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>33156</v>
+        <v>33347</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>692</v>
+        <v>612</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>33193</v>
+        <v>33356</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>682</v>
+        <v>616</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>33199</v>
+        <v>33366</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>688</v>
+        <v>600</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>33201</v>
+        <v>33368</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>33221</v>
+        <v>33370</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>682</v>
+        <v>600</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>33242</v>
+        <v>33396</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>689</v>
+        <v>605</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>33263</v>
+        <v>33407</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>675</v>
+        <v>588</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>33337</v>
+        <v>33412</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>33347</v>
+        <v>33432</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>689</v>
+        <v>588</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>33356</v>
+        <v>33436</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>693</v>
+        <v>600</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>33366</v>
+        <v>33444</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>33368</v>
+        <v>33451</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>33370</v>
+        <v>33463</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>677</v>
+        <v>590</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>33396</v>
+        <v>33470</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>182</v>
+        <v>37</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>682</v>
+        <v>595</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>33407</v>
+        <v>33475</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>664</v>
+        <v>599</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>33412</v>
+        <v>33482</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>677</v>
+        <v>599</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>33432</v>
+        <v>33528</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>664</v>
+        <v>591</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>33436</v>
+        <v>33531</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>677</v>
+        <v>587</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>33444</v>
+        <v>33545</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>33451</v>
+        <v>33563</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>682</v>
+        <v>600</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>33463</v>
+        <v>33565</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>666</v>
+        <v>588</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>33127</v>
+        <v>33569</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>33475</v>
+        <v>33640</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>33482</v>
+        <v>33642</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>33528</v>
+        <v>33653</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>667</v>
+        <v>615</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>33531</v>
+        <v>33686</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>663</v>
+        <v>612</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>33545</v>
+        <v>33763</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>33561</v>
+        <v>33802</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>677</v>
+        <v>622</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>33563</v>
+        <v>33807</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>677</v>
+        <v>617</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>33565</v>
+        <v>33836</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>664</v>
+        <v>600</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>33569</v>
+        <v>33848</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>33618</v>
+        <v>33959</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>694</v>
+        <v>590</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>33640</v>
+        <v>33965</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>33642</v>
+        <v>34016</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>677</v>
+        <v>588</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>33653</v>
+        <v>34027</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>692</v>
+        <v>590</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>33686</v>
+        <v>34068</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>689</v>
+        <v>588</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>33763</v>
+        <v>34070</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>675</v>
+        <v>591</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>33802</v>
+        <v>34102</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>33807</v>
+        <v>34115</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>695</v>
+        <v>598</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>33836</v>
+        <v>34167</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>677</v>
+        <v>605</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>33848</v>
+        <v>34168</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>677</v>
+        <v>618</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>33959</v>
+        <v>34636</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>666</v>
+        <v>600</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>33965</v>
+        <v>34637</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>34016</v>
+        <v>34640</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>664</v>
+        <v>600</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>34027</v>
+        <v>34696</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>666</v>
+        <v>598</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>34068</v>
+        <v>34749</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>664</v>
+        <v>617</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>34070</v>
+        <v>34768</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>667</v>
+        <v>600</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>34102</v>
+        <v>34773</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>677</v>
+        <v>590</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>34115</v>
+        <v>34774</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>34167</v>
+        <v>34776</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>682</v>
+        <v>600</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>34168</v>
+        <v>34824</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>696</v>
+        <v>598</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>34636</v>
+        <v>34826</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>677</v>
+        <v>619</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>34637</v>
+        <v>34955</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>675</v>
+        <v>590</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>34640</v>
+        <v>35002</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>34696</v>
+        <v>35003</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>34704</v>
+        <v>35027</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>34749</v>
+        <v>35083</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>695</v>
+        <v>588</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>34768</v>
+        <v>35161</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>677</v>
+        <v>620</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>34773</v>
+        <v>35220</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>666</v>
+        <v>619</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>34774</v>
+        <v>35310</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>34776</v>
+        <v>35353</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>34783</v>
+        <v>35356</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>34824</v>
+        <v>35367</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>34826</v>
+        <v>35384</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>697</v>
+        <v>600</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>34906</v>
+        <v>35398</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>34937</v>
+        <v>35457</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>677</v>
+        <v>621</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>34955</v>
+        <v>35551</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>666</v>
+        <v>610</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>35002</v>
+        <v>35555</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>35003</v>
+        <v>35583</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>675</v>
+        <v>608</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>35027</v>
+        <v>35585</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>35083</v>
+        <v>35635</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>664</v>
+        <v>598</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>35161</v>
+        <v>35663</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>698</v>
+        <v>591</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>35220</v>
+        <v>35690</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>697</v>
+        <v>598</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
-        <v>35310</v>
+        <v>35790</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>677</v>
+        <v>622</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
-        <v>35353</v>
+        <v>35817</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>35356</v>
+        <v>35878</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>677</v>
+        <v>609</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>35367</v>
+        <v>35893</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>675</v>
+        <v>617</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>35384</v>
+        <v>35905</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>677</v>
+        <v>609</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>35398</v>
+        <v>35927</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>675</v>
+        <v>605</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>35457</v>
+        <v>35959</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>699</v>
+        <v>598</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>35551</v>
+        <v>35966</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>687</v>
+        <v>598</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>35555</v>
+        <v>35973</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>677</v>
+        <v>602</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>35583</v>
+        <v>35981</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>685</v>
+        <v>605</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>35585</v>
+        <v>35983</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>35635</v>
+        <v>35988</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>253</v>
+        <v>536</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>35663</v>
+        <v>36005</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>667</v>
+        <v>598</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>35690</v>
+        <v>36037</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>35790</v>
+        <v>36053</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>700</v>
+        <v>605</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
-        <v>35817</v>
+        <v>36056</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>677</v>
+        <v>602</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
-        <v>35878</v>
+        <v>36057</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>686</v>
+        <v>598</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>35893</v>
+        <v>36062</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>695</v>
+        <v>598</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>35905</v>
+        <v>36108</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>686</v>
+        <v>598</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>35927</v>
+        <v>36120</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>675</v>
+        <v>605</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>35959</v>
+        <v>36133</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>35964</v>
+        <v>36168</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>680</v>
+        <v>598</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
-        <v>35966</v>
+        <v>36220</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>35973</v>
+        <v>36223</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>35981</v>
+        <v>36225</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>35983</v>
+        <v>36226</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>36223</v>
+        <v>36255</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>689</v>
+        <v>605</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>35997</v>
+        <v>36258</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>675</v>
+        <v>615</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>36005</v>
+        <v>36259</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>675</v>
+        <v>622</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>36037</v>
+        <v>36267</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>36042</v>
+        <v>36271</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>36053</v>
+        <v>36272</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>36056</v>
+        <v>36274</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>36057</v>
+        <v>36281</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>36062</v>
+        <v>36373</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>675</v>
+        <v>617</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>36108</v>
+        <v>36390</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>36120</v>
+        <v>36398</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>36133</v>
+        <v>37401</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>675</v>
+        <v>608</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>36168</v>
+        <v>37567</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>36220</v>
+        <v>38220</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>36267</v>
+        <v>38244</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>689</v>
+        <v>611</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>36225</v>
+        <v>38247</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>675</v>
+        <v>610</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>36226</v>
+        <v>38279</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>689</v>
+        <v>599</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>36255</v>
+        <v>38282</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>682</v>
+        <v>599</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>36258</v>
+        <v>38330</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>692</v>
+        <v>609</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>36259</v>
+        <v>38331</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>700</v>
+        <v>609</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>39942</v>
+        <v>38335</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>689</v>
+        <v>610</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
-        <v>36271</v>
+        <v>38350</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>677</v>
+        <v>609</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
-        <v>36272</v>
+        <v>38351</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>677</v>
+        <v>609</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
-        <v>36274</v>
+        <v>38379</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>677</v>
+        <v>609</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
-        <v>36281</v>
+        <v>38420</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>689</v>
+        <v>611</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
-        <v>36373</v>
+        <v>38429</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>695</v>
+        <v>608</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
-        <v>36390</v>
+        <v>38472</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>677</v>
+        <v>610</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
-        <v>36398</v>
+        <v>38486</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>677</v>
+        <v>599</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
-        <v>37401</v>
+        <v>38489</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>296</v>
+        <v>427</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>685</v>
+        <v>599</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
-        <v>40971</v>
+        <v>38506</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>689</v>
+        <v>609</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
-        <v>37567</v>
+        <v>38519</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>677</v>
+        <v>608</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
-        <v>37653</v>
+        <v>38522</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>677</v>
+        <v>608</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
-        <v>38220</v>
+        <v>38523</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>677</v>
+        <v>610</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
-        <v>38244</v>
+        <v>38555</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>301</v>
+        <v>128</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>688</v>
+        <v>600</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
-        <v>38247</v>
+        <v>38565</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>687</v>
+        <v>609</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
-        <v>38279</v>
+        <v>38566</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>676</v>
+        <v>610</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
-        <v>38282</v>
+        <v>38568</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>676</v>
+        <v>609</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
-        <v>38330</v>
+        <v>38610</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>686</v>
+        <v>600</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
-        <v>38331</v>
+        <v>38611</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>686</v>
+        <v>600</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
-        <v>38335</v>
+        <v>38617</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>687</v>
+        <v>600</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
-        <v>38350</v>
+        <v>38619</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>686</v>
+        <v>600</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
-        <v>38351</v>
+        <v>38626</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>686</v>
+        <v>610</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
-        <v>38371</v>
+        <v>38629</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>687</v>
+        <v>609</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
-        <v>38379</v>
+        <v>38630</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>686</v>
+        <v>598</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
-        <v>38420</v>
+        <v>38634</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>688</v>
+        <v>598</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
-        <v>38429</v>
+        <v>38895</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>685</v>
+        <v>609</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
-        <v>38472</v>
+        <v>38897</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>687</v>
+        <v>598</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
-        <v>38486</v>
+        <v>39029</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
-        <v>40990</v>
+        <v>39040</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>689</v>
+        <v>621</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
-        <v>38506</v>
+        <v>39064</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>686</v>
+        <v>598</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
-        <v>38510</v>
+        <v>39065</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>685</v>
+        <v>598</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
-        <v>38519</v>
+        <v>39070</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>685</v>
+        <v>616</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
-        <v>38522</v>
+        <v>39071</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>685</v>
+        <v>612</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
-        <v>38523</v>
+        <v>39072</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>687</v>
+        <v>612</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
-        <v>41894</v>
+        <v>39073</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
-        <v>38565</v>
+        <v>39074</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>686</v>
+        <v>609</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
-        <v>38566</v>
+        <v>39117</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>687</v>
+        <v>600</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
-        <v>38567</v>
+        <v>39123</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>686</v>
+        <v>623</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
-        <v>38568</v>
+        <v>39127</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>686</v>
+        <v>612</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
-        <v>38610</v>
+        <v>39144</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
-        <v>38611</v>
+        <v>39153</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
-        <v>38617</v>
+        <v>39168</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>677</v>
+        <v>599</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
-        <v>38619</v>
+        <v>39174</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
-        <v>38626</v>
+        <v>39186</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>687</v>
+        <v>622</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
-        <v>38629</v>
+        <v>39205</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>686</v>
+        <v>600</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
-        <v>38630</v>
+        <v>39208</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
-        <v>38634</v>
+        <v>39210</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
-        <v>38895</v>
+        <v>39211</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>686</v>
+        <v>612</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
-        <v>38897</v>
+        <v>39212</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
-        <v>38905</v>
+        <v>39222</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
-        <v>39028</v>
+        <v>39225</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
-        <v>39029</v>
+        <v>39230</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
-        <v>39040</v>
+        <v>39249</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>699</v>
+        <v>600</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
-        <v>39064</v>
+        <v>39254</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
-        <v>39065</v>
+        <v>39337</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
-        <v>39070</v>
+        <v>39390</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>693</v>
+        <v>624</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
-        <v>39071</v>
+        <v>39391</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
-        <v>39072</v>
+        <v>39462</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>689</v>
+        <v>623</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
-        <v>39073</v>
+        <v>39467</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>689</v>
+        <v>601</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
-        <v>39074</v>
+        <v>39586</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>686</v>
+        <v>622</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
-        <v>39117</v>
+        <v>39588</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>677</v>
+        <v>622</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
-        <v>39123</v>
+        <v>39781</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>701</v>
+        <v>600</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
-        <v>39127</v>
+        <v>39785</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
-        <v>39144</v>
+        <v>39788</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
-        <v>39153</v>
+        <v>39806</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
-        <v>39168</v>
+        <v>39807</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>676</v>
+        <v>612</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
-        <v>39174</v>
+        <v>39816</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
-        <v>39186</v>
+        <v>39817</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>700</v>
+        <v>612</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
-        <v>39205</v>
+        <v>39821</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
-        <v>39208</v>
+        <v>39829</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
-        <v>39210</v>
+        <v>39830</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
-        <v>39211</v>
+        <v>39835</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>689</v>
+        <v>599</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
-        <v>39212</v>
+        <v>39836</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>689</v>
+        <v>599</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
-        <v>39222</v>
+        <v>39837</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>675</v>
+        <v>599</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
-        <v>39225</v>
+        <v>39849</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
-        <v>39230</v>
+        <v>39852</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
-        <v>39249</v>
+        <v>39853</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
-        <v>39254</v>
+        <v>39857</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
-        <v>39337</v>
+        <v>39858</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
-        <v>39390</v>
+        <v>39864</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>702</v>
+        <v>598</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
-        <v>39391</v>
+        <v>39865</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>702</v>
+        <v>598</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
-        <v>39462</v>
+        <v>39866</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>701</v>
+        <v>600</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
-        <v>39467</v>
+        <v>39872</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>678</v>
+        <v>599</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
-        <v>39474</v>
+        <v>39884</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>676</v>
+        <v>599</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
-        <v>39586</v>
+        <v>39888</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>700</v>
+        <v>612</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
-        <v>39587</v>
+        <v>39894</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>700</v>
+        <v>598</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
-        <v>39588</v>
+        <v>39896</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
-        <v>39781</v>
+        <v>39901</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>677</v>
+        <v>624</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
-        <v>39785</v>
+        <v>39902</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>677</v>
+        <v>599</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
-        <v>39788</v>
+        <v>39904</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>677</v>
+        <v>599</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
-        <v>39806</v>
+        <v>39907</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
-        <v>39807</v>
+        <v>39908</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
-        <v>39816</v>
+        <v>39913</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
-        <v>39817</v>
+        <v>39914</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
-        <v>39821</v>
+        <v>39915</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
-        <v>39829</v>
+        <v>39916</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
-        <v>39830</v>
+        <v>39919</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
-        <v>39835</v>
+        <v>39924</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>676</v>
+        <v>624</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
-        <v>39836</v>
+        <v>39929</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
-        <v>39837</v>
+        <v>39931</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
-        <v>39845</v>
+        <v>39941</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
-        <v>39849</v>
+        <v>39942</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>389</v>
+        <v>268</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
-        <v>39851</v>
+        <v>39954</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
-        <v>39852</v>
+        <v>39956</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
-        <v>39853</v>
+        <v>39976</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
-        <v>39857</v>
+        <v>39980</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
-        <v>39858</v>
+        <v>39981</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
-        <v>39864</v>
+        <v>39984</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>675</v>
+        <v>624</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
-        <v>39865</v>
+        <v>39991</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
-        <v>39866</v>
+        <v>39993</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
-        <v>39872</v>
+        <v>40006</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>676</v>
+        <v>598</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
-        <v>39884</v>
+        <v>40008</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>676</v>
+        <v>598</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
-        <v>39885</v>
+        <v>40032</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
-        <v>39888</v>
+        <v>40062</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
-        <v>39892</v>
+        <v>40072</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>687</v>
+        <v>598</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
-        <v>39894</v>
+        <v>40111</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>675</v>
+        <v>599</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
-        <v>39896</v>
+        <v>40348</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
-        <v>39901</v>
+        <v>40504</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>702</v>
+        <v>598</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
-        <v>39902</v>
+        <v>40509</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>676</v>
+        <v>625</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
-        <v>39904</v>
+        <v>40558</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
-        <v>39907</v>
+        <v>40774</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
-        <v>39908</v>
+        <v>40775</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
-        <v>39913</v>
+        <v>40776</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
-        <v>39914</v>
+        <v>40777</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
-        <v>39915</v>
+        <v>40836</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>702</v>
+        <v>600</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
-        <v>39916</v>
+        <v>40837</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
-        <v>39917</v>
+        <v>40838</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
-        <v>39919</v>
+        <v>40843</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
-        <v>39924</v>
+        <v>40854</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>702</v>
+        <v>610</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
-        <v>39929</v>
+        <v>40861</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>677</v>
+        <v>607</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
-        <v>39930</v>
+        <v>40872</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
-        <v>39931</v>
+        <v>40875</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
-        <v>39933</v>
+        <v>40880</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>687</v>
+        <v>624</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
-        <v>39941</v>
+        <v>40881</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
-        <v>30885</v>
+        <v>40883</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>666</v>
+        <v>608</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
-        <v>39953</v>
+        <v>40887</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>702</v>
+        <v>600</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
-        <v>39954</v>
+        <v>40925</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>677</v>
+        <v>610</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
-        <v>39955</v>
+        <v>40956</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>677</v>
+        <v>626</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
-        <v>39956</v>
+        <v>40958</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
-        <v>39976</v>
+        <v>40971</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>427</v>
+        <v>277</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
-        <v>39980</v>
+        <v>40980</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
-        <v>39981</v>
+        <v>40981</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
-        <v>39984</v>
+        <v>40992</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
-        <v>39991</v>
+        <v>41007</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>689</v>
+        <v>610</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
-        <v>39993</v>
+        <v>41008</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
-        <v>39995</v>
+        <v>41009</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
-        <v>40006</v>
+        <v>41010</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
-        <v>40008</v>
+        <v>41011</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
-        <v>40009</v>
+        <v>41089</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
-        <v>40032</v>
+        <v>41149</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
-        <v>40062</v>
+        <v>41150</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
-        <v>40072</v>
+        <v>41152</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
-        <v>40111</v>
+        <v>41156</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>676</v>
+        <v>600</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
-        <v>40193</v>
+        <v>41185</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
-        <v>40348</v>
+        <v>41187</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
-        <v>40504</v>
+        <v>41190</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
-        <v>40509</v>
+        <v>41194</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>703</v>
+        <v>600</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
-        <v>40558</v>
+        <v>41200</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
-        <v>40774</v>
+        <v>41208</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
-        <v>40775</v>
+        <v>41217</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
-        <v>40776</v>
+        <v>41237</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
-        <v>40777</v>
+        <v>41271</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
-        <v>40836</v>
+        <v>41286</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
-        <v>40837</v>
+        <v>41289</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
-        <v>40838</v>
+        <v>41295</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
-        <v>40843</v>
+        <v>41298</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
-        <v>40854</v>
+        <v>41305</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>687</v>
+        <v>600</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
-        <v>40861</v>
+        <v>41318</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>684</v>
+        <v>600</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
-        <v>40872</v>
+        <v>41321</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
-        <v>40875</v>
+        <v>41332</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>689</v>
+        <v>599</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
-        <v>40880</v>
+        <v>41350</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>702</v>
+        <v>624</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
-        <v>40881</v>
+        <v>41355</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>702</v>
+        <v>627</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
-        <v>40883</v>
+        <v>41371</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>685</v>
+        <v>624</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
-        <v>40887</v>
+        <v>41373</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>677</v>
+        <v>610</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
-        <v>40925</v>
+        <v>41376</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>687</v>
+        <v>600</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
-        <v>40941</v>
+        <v>41377</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>675</v>
+        <v>599</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
-        <v>40956</v>
+        <v>41383</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>704</v>
+        <v>599</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
-        <v>40958</v>
+        <v>41384</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>689</v>
+        <v>599</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
-        <v>31335</v>
+        <v>41392</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>676</v>
+        <v>604</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
-        <v>40980</v>
+        <v>41415</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
-        <v>40981</v>
+        <v>41420</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C467" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
-        <v>38489</v>
+        <v>41429</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C468" s="1" t="s">
-        <v>676</v>
+        <v>624</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
-        <v>40992</v>
+        <v>41430</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C469" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
-        <v>41003</v>
+        <v>41432</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C470" s="1" t="s">
-        <v>685</v>
+        <v>600</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
-        <v>41006</v>
+        <v>41438</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C471" s="1" t="s">
-        <v>702</v>
+        <v>609</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
-        <v>41007</v>
+        <v>41439</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C472" s="1" t="s">
-        <v>687</v>
+        <v>624</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
-        <v>41008</v>
+        <v>41449</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>689</v>
+        <v>610</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
-        <v>41009</v>
+        <v>41451</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C474" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
-        <v>41010</v>
+        <v>41470</v>
       </c>
       <c r="B475" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C475" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
-        <v>41011</v>
+        <v>41484</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C476" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
-        <v>41019</v>
+        <v>41507</v>
       </c>
       <c r="B477" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C477" s="1" t="s">
-        <v>677</v>
+        <v>595</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
-        <v>41039</v>
+        <v>41527</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C478" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
-        <v>41049</v>
+        <v>41528</v>
       </c>
       <c r="B479" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>686</v>
+        <v>600</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
-        <v>41089</v>
+        <v>41530</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C480" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
-        <v>41149</v>
+        <v>41538</v>
       </c>
       <c r="B481" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
-        <v>41150</v>
+        <v>41539</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C482" s="1" t="s">
-        <v>689</v>
+        <v>609</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
-        <v>41152</v>
+        <v>41542</v>
       </c>
       <c r="B483" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C483" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
-        <v>41156</v>
+        <v>41543</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C484" s="1" t="s">
-        <v>677</v>
+        <v>609</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
-        <v>41185</v>
+        <v>41571</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C485" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
-        <v>41187</v>
+        <v>41572</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
-        <v>41190</v>
+        <v>41597</v>
       </c>
       <c r="B487" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C487" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
-        <v>41194</v>
+        <v>41599</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C488" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
-        <v>41200</v>
+        <v>41603</v>
       </c>
       <c r="B489" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C489" s="1" t="s">
-        <v>689</v>
+        <v>595</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
-        <v>41208</v>
+        <v>41605</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C490" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
-        <v>41217</v>
+        <v>41608</v>
       </c>
       <c r="B491" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
-        <v>41234</v>
+        <v>41615</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C492" s="1" t="s">
-        <v>680</v>
+        <v>609</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
-        <v>41237</v>
+        <v>41618</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
-        <v>41243</v>
+        <v>41627</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C494" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
-        <v>41244</v>
+        <v>41633</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
-        <v>41245</v>
+        <v>41643</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
-        <v>41271</v>
+        <v>41644</v>
       </c>
       <c r="B497" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C497" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
-        <v>41286</v>
+        <v>41655</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C498" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
-        <v>41289</v>
+        <v>41659</v>
       </c>
       <c r="B499" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C499" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
-        <v>41295</v>
+        <v>41669</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C500" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
-        <v>41298</v>
+        <v>41675</v>
       </c>
       <c r="B501" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C501" s="1" t="s">
-        <v>675</v>
+        <v>608</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
-        <v>41303</v>
+        <v>41684</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C502" s="1" t="s">
-        <v>677</v>
+        <v>628</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
-        <v>41305</v>
+        <v>41711</v>
       </c>
       <c r="B503" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C503" s="1" t="s">
-        <v>677</v>
+        <v>624</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
-        <v>41318</v>
+        <v>41725</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>505</v>
+        <v>550</v>
       </c>
       <c r="C504" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
-        <v>41321</v>
+        <v>41731</v>
       </c>
       <c r="B505" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C505" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
-        <v>41332</v>
+        <v>41737</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C506" s="1" t="s">
-        <v>676</v>
+        <v>612</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
-        <v>41339</v>
+        <v>41738</v>
       </c>
       <c r="B507" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C507" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
-        <v>41350</v>
+        <v>41739</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C508" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
-        <v>41355</v>
+        <v>41744</v>
       </c>
       <c r="B509" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C509" s="1" t="s">
-        <v>705</v>
+        <v>612</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
-        <v>41371</v>
+        <v>41745</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C510" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
-        <v>41373</v>
+        <v>41748</v>
       </c>
       <c r="B511" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C511" s="1" t="s">
-        <v>687</v>
+        <v>612</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
-        <v>30963</v>
+        <v>41754</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C512" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
-        <v>41376</v>
+        <v>41756</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C513" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
-        <v>41377</v>
+        <v>41772</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>676</v>
+        <v>598</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
-        <v>41383</v>
+        <v>41773</v>
       </c>
       <c r="B515" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>676</v>
+        <v>598</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
-        <v>41384</v>
+        <v>41776</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>676</v>
+        <v>628</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
-        <v>41392</v>
+        <v>41799</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>681</v>
+        <v>624</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
-        <v>41410</v>
+        <v>41806</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C518" s="1" t="s">
-        <v>687</v>
+        <v>612</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
-        <v>41415</v>
+        <v>41807</v>
       </c>
       <c r="B519" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C519" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
-        <v>41420</v>
+        <v>41808</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C520" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
-        <v>41425</v>
+        <v>41815</v>
       </c>
       <c r="B521" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C521" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
-        <v>41429</v>
+        <v>41816</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C522" s="1" t="s">
-        <v>702</v>
+        <v>624</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
-        <v>41430</v>
+        <v>41817</v>
       </c>
       <c r="B523" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C523" s="1" t="s">
-        <v>702</v>
+        <v>624</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
-        <v>41432</v>
+        <v>41825</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C524" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
-        <v>41438</v>
+        <v>41828</v>
       </c>
       <c r="B525" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C525" s="1" t="s">
-        <v>686</v>
+        <v>600</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
-        <v>41439</v>
+        <v>41837</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C526" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
-        <v>41444</v>
+        <v>41841</v>
       </c>
       <c r="B527" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C527" s="1" t="s">
-        <v>666</v>
+        <v>608</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
-        <v>41449</v>
+        <v>41842</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C528" s="1" t="s">
-        <v>687</v>
+        <v>612</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
-        <v>41451</v>
+        <v>41846</v>
       </c>
       <c r="B529" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C529" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
-        <v>41470</v>
+        <v>41851</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C530" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
-        <v>41484</v>
+        <v>41877</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C531" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
-        <v>41490</v>
+        <v>41879</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C532" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
-        <v>41507</v>
+        <v>41885</v>
       </c>
       <c r="B533" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C533" s="1" t="s">
-        <v>671</v>
+        <v>612</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
-        <v>41527</v>
+        <v>41886</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C534" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
-        <v>41528</v>
+        <v>41893</v>
       </c>
       <c r="B535" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C535" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
-        <v>41530</v>
+        <v>41894</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>537</v>
+        <v>298</v>
       </c>
       <c r="C536" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
-        <v>41538</v>
+        <v>41902</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C537" s="1" t="s">
-        <v>677</v>
+        <v>600</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
-        <v>41539</v>
+        <v>41912</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>686</v>
+        <v>624</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
-        <v>41542</v>
+        <v>41946</v>
       </c>
       <c r="B539" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C539" s="1" t="s">
-        <v>702</v>
+        <v>598</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
-        <v>41543</v>
+        <v>41947</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C540" s="1" t="s">
-        <v>686</v>
+        <v>598</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
-        <v>41571</v>
+        <v>41948</v>
       </c>
       <c r="B541" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C541" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
-        <v>41572</v>
+        <v>41949</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C542" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" s="1">
-        <v>41597</v>
+        <v>41950</v>
       </c>
       <c r="B543" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C543" s="1" t="s">
-        <v>677</v>
+        <v>612</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" s="1">
-        <v>41598</v>
+        <v>41951</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C544" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" s="1">
-        <v>41599</v>
+        <v>41953</v>
       </c>
       <c r="B545" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C545" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" s="1">
-        <v>41603</v>
+        <v>41954</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C546" s="1" t="s">
-        <v>671</v>
+        <v>598</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" s="1">
-        <v>41605</v>
+        <v>41963</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C547" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" s="1">
-        <v>41608</v>
+        <v>41965</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C548" s="1" t="s">
-        <v>702</v>
+        <v>612</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" s="1">
-        <v>41615</v>
+        <v>41966</v>
       </c>
       <c r="B549" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C549" s="1" t="s">
-        <v>686</v>
+        <v>612</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" s="1">
-        <v>41618</v>
+        <v>41975</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>551</v>
       </c>
       <c r="C550" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" s="1">
-        <v>41627</v>
+        <v>41979</v>
       </c>
       <c r="B551" s="1" t="s">
         <v>552</v>
       </c>
       <c r="C551" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" s="1">
-        <v>41633</v>
+        <v>41983</v>
       </c>
       <c r="B552" s="1" t="s">
         <v>553</v>
       </c>
       <c r="C552" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553" s="1">
-        <v>41643</v>
+        <v>41984</v>
       </c>
       <c r="B553" s="1" t="s">
         <v>554</v>
       </c>
       <c r="C553" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554" s="1">
-        <v>41644</v>
+        <v>41986</v>
       </c>
       <c r="B554" s="1" t="s">
         <v>555</v>
       </c>
       <c r="C554" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555" s="1">
-        <v>41655</v>
+        <v>42008</v>
       </c>
       <c r="B555" s="1" t="s">
         <v>556</v>
       </c>
       <c r="C555" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556" s="1">
-        <v>41657</v>
+        <v>42014</v>
       </c>
       <c r="B556" s="1" t="s">
         <v>557</v>
       </c>
       <c r="C556" s="1" t="s">
-        <v>687</v>
+        <v>624</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557" s="1">
-        <v>41659</v>
+        <v>42018</v>
       </c>
       <c r="B557" s="1" t="s">
         <v>558</v>
       </c>
       <c r="C557" s="1" t="s">
-        <v>675</v>
+        <v>600</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558" s="1">
-        <v>41669</v>
+        <v>42035</v>
       </c>
       <c r="B558" s="1" t="s">
         <v>559</v>
       </c>
       <c r="C558" s="1" t="s">
-        <v>675</v>
+        <v>622</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559" s="1">
-        <v>41675</v>
+        <v>42036</v>
       </c>
       <c r="B559" s="1" t="s">
         <v>560</v>
       </c>
       <c r="C559" s="1" t="s">
-        <v>685</v>
+        <v>612</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560" s="1">
-        <v>41684</v>
+        <v>42039</v>
       </c>
       <c r="B560" s="1" t="s">
         <v>561</v>
       </c>
       <c r="C560" s="1" t="s">
-        <v>706</v>
+        <v>598</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561" s="1">
-        <v>41711</v>
+        <v>42040</v>
       </c>
       <c r="B561" s="1" t="s">
         <v>562</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>702</v>
+        <v>624</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562" s="1">
-        <v>32055</v>
+        <v>42070</v>
       </c>
       <c r="B562" s="1" t="s">
         <v>563</v>
       </c>
       <c r="C562" s="1" t="s">
-        <v>675</v>
+        <v>612</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563" s="1">
-        <v>41731</v>
+        <v>42074</v>
       </c>
       <c r="B563" s="1" t="s">
-        <v>564</v>
+        <v>631</v>
       </c>
       <c r="C563" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564" s="1">
-        <v>41735</v>
+        <v>42076</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C564" s="1" t="s">
-        <v>682</v>
+        <v>624</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565" s="1">
-        <v>41737</v>
+        <v>42084</v>
       </c>
       <c r="B565" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C565" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566" s="1">
-        <v>41738</v>
+        <v>42087</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C566" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567" s="1">
-        <v>41739</v>
+        <v>42544</v>
       </c>
       <c r="B567" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C567" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568" s="1">
-        <v>41744</v>
+        <v>42546</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C568" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569" s="1">
-        <v>41745</v>
+        <v>42547</v>
       </c>
       <c r="B569" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C569" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570" s="1">
-        <v>41748</v>
+        <v>42556</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C570" s="1" t="s">
-        <v>689</v>
+        <v>624</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571" s="1">
-        <v>41753</v>
+        <v>42574</v>
       </c>
       <c r="B571" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C571" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572" s="1">
-        <v>41754</v>
+        <v>42576</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C572" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573" s="1">
-        <v>41756</v>
+        <v>42580</v>
       </c>
       <c r="B573" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C573" s="1" t="s">
-        <v>677</v>
+        <v>624</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574" s="1">
-        <v>41772</v>
+        <v>42583</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C574" s="1" t="s">
-        <v>675</v>
+        <v>624</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" s="1">
-        <v>41773</v>
+        <v>42614</v>
       </c>
       <c r="B575" s="1" t="s">
-        <v>576</v>
+        <v>632</v>
       </c>
       <c r="C575" s="1" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576" s="1">
-        <v>41776</v>
+        <v>42650</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C576" s="1" t="s">
-        <v>706</v>
+        <v>600</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577" s="1">
-        <v>41799</v>
+        <v>42651</v>
       </c>
       <c r="B577" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C577" s="1" t="s">
-        <v>702</v>
+        <v>600</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578" s="1">
-        <v>41806</v>
+        <v>42655</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C578" s="1" t="s">
-        <v>689</v>
+        <v>612</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" s="1">
-        <v>41807</v>
+        <v>42668</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>580</v>
+        <v>633</v>
       </c>
       <c r="C579" s="1" t="s">
-        <v>689</v>
+        <v>598</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580" s="1">
-        <v>41808</v>
+        <v>42670</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C580" s="1" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" s="1">
-        <v>41809</v>
+        <v>42671</v>
       </c>
       <c r="B581" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C581" s="1" t="s">
-        <v>682</v>
+        <v>600</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" s="1">
-        <v>41815</v>
+        <v>42704</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C582" s="1" t="s">
-        <v>689</v>
+        <v>609</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583" s="1">
-        <v>41816</v>
+        <v>42712</v>
       </c>
       <c r="B583" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C583" s="1" t="s">
-        <v>702</v>
+        <v>587</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584" s="1">
-        <v>41817</v>
+        <v>42713</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>585</v>
+        <v>634</v>
       </c>
       <c r="C584" s="1" t="s">
-        <v>702</v>
+        <v>598</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585" s="1">
-        <v>41821</v>
+        <v>42753</v>
       </c>
       <c r="B585" s="1" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>677</v>
+        <v>598</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" s="1">
-        <v>41825</v>
+        <v>42777</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C586" s="1" t="s">
-        <v>677</v>
+        <v>604</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587" s="1">
-        <v>41828</v>
+        <v>42817</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C587" s="1" t="s">
-        <v>677</v>
+        <v>587</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588" s="1">
-        <v>41829</v>
+        <v>42936</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>589</v>
+        <v>635</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>675</v>
+        <v>595</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589" s="1">
-        <v>41837</v>
+        <v>43008</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>590</v>
+        <v>636</v>
       </c>
       <c r="C589" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A590" s="1">
-        <v>41841</v>
-      </c>
-      <c r="B590" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="C590" s="1" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A591" s="1">
-        <v>41842</v>
-      </c>
-      <c r="B591" s="1" t="s">
-        <v>592</v>
-      </c>
-      <c r="C591" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A592" s="1">
-        <v>41844</v>
-      </c>
-      <c r="B592" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="C592" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A593" s="1">
-        <v>41846</v>
-      </c>
-      <c r="B593" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="C593" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A594" s="1">
-        <v>41851</v>
-      </c>
-      <c r="B594" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="C594" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A595" s="1">
-        <v>41876</v>
-      </c>
-      <c r="B595" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A596" s="1">
-        <v>41877</v>
-      </c>
-      <c r="B596" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="C596" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A597" s="1">
-        <v>41879</v>
-      </c>
-      <c r="B597" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="C597" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A598" s="1">
-        <v>41882</v>
-      </c>
-      <c r="B598" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="C598" s="1" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A599" s="1">
-        <v>41885</v>
-      </c>
-      <c r="B599" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="C599" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A600" s="1">
-        <v>41886</v>
-      </c>
-      <c r="B600" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="C600" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A601" s="1">
-        <v>41892</v>
-      </c>
-      <c r="B601" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="C601" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A602" s="1">
-        <v>41893</v>
-      </c>
-      <c r="B602" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="C602" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A603" s="1">
-        <v>35988</v>
-      </c>
-      <c r="B603" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="C603" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A604" s="1">
-        <v>41902</v>
-      </c>
-      <c r="B604" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="C604" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A605" s="1">
-        <v>41912</v>
-      </c>
-      <c r="B605" s="1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C605" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A606" s="1">
-        <v>41914</v>
-      </c>
-      <c r="B606" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="C606" s="1" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A607" s="1">
-        <v>41919</v>
-      </c>
-      <c r="B607" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="C607" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A608" s="1">
-        <v>41924</v>
-      </c>
-      <c r="B608" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="C608" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A609" s="1">
-        <v>41946</v>
-      </c>
-      <c r="B609" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="C609" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A610" s="1">
-        <v>41947</v>
-      </c>
-      <c r="B610" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="C610" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A611" s="1">
-        <v>41948</v>
-      </c>
-      <c r="B611" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="C611" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A612" s="1">
-        <v>41949</v>
-      </c>
-      <c r="B612" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="C612" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A613" s="1">
-        <v>41950</v>
-      </c>
-      <c r="B613" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="C613" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A614" s="1">
-        <v>41951</v>
-      </c>
-      <c r="B614" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="C614" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A615" s="1">
-        <v>41952</v>
-      </c>
-      <c r="B615" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="C615" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A616" s="1">
-        <v>41953</v>
-      </c>
-      <c r="B616" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="C616" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A617" s="1">
-        <v>41954</v>
-      </c>
-      <c r="B617" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="C617" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A618" s="1">
-        <v>41963</v>
-      </c>
-      <c r="B618" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="C618" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A619" s="1">
-        <v>41964</v>
-      </c>
-      <c r="B619" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="C619" s="1" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A620" s="1">
-        <v>41965</v>
-      </c>
-      <c r="B620" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="C620" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A621" s="1">
-        <v>41966</v>
-      </c>
-      <c r="B621" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="C621" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A622" s="1">
-        <v>41725</v>
-      </c>
-      <c r="B622" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="C622" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A623" s="1">
-        <v>41975</v>
-      </c>
-      <c r="B623" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="C623" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A624" s="1">
-        <v>41979</v>
-      </c>
-      <c r="B624" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="C624" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A625" s="1">
-        <v>41983</v>
-      </c>
-      <c r="B625" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="C625" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A626" s="1">
-        <v>41984</v>
-      </c>
-      <c r="B626" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C626" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A627" s="1">
-        <v>41986</v>
-      </c>
-      <c r="B627" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="C627" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A628" s="1">
-        <v>42008</v>
-      </c>
-      <c r="B628" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="C628" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A629" s="1">
-        <v>42014</v>
-      </c>
-      <c r="B629" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="C629" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A630" s="1">
-        <v>42018</v>
-      </c>
-      <c r="B630" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="C630" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A631" s="1">
-        <v>42033</v>
-      </c>
-      <c r="B631" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C631" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A632" s="1">
-        <v>42035</v>
-      </c>
-      <c r="B632" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="C632" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A633" s="1">
-        <v>42036</v>
-      </c>
-      <c r="B633" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="C633" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A634" s="1">
-        <v>42039</v>
-      </c>
-      <c r="B634" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C634" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A635" s="1">
-        <v>42040</v>
-      </c>
-      <c r="B635" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="C635" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A636" s="1">
-        <v>42070</v>
-      </c>
-      <c r="B636" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="C636" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A637" s="1">
-        <v>42076</v>
-      </c>
-      <c r="B637" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="C637" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A638" s="1">
-        <v>42084</v>
-      </c>
-      <c r="B638" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="C638" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A639" s="1">
-        <v>42087</v>
-      </c>
-      <c r="B639" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="C639" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A640" s="1">
-        <v>42544</v>
-      </c>
-      <c r="B640" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="C640" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A641" s="1">
-        <v>42546</v>
-      </c>
-      <c r="B641" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="C641" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A642" s="1">
-        <v>42547</v>
-      </c>
-      <c r="B642" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="C642" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A643" s="1">
-        <v>42556</v>
-      </c>
-      <c r="B643" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="C643" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A644" s="1">
-        <v>42574</v>
-      </c>
-      <c r="B644" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="C644" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A645" s="1">
-        <v>42575</v>
-      </c>
-      <c r="B645" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="C645" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A646" s="1">
-        <v>42576</v>
-      </c>
-      <c r="B646" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="C646" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A647" s="1">
-        <v>42580</v>
-      </c>
-      <c r="B647" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="C647" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A648" s="1">
-        <v>42583</v>
-      </c>
-      <c r="B648" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C648" s="1" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A649" s="1">
-        <v>42650</v>
-      </c>
-      <c r="B649" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="C649" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A650" s="1">
-        <v>42651</v>
-      </c>
-      <c r="B650" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C650" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A651" s="1">
-        <v>42655</v>
-      </c>
-      <c r="B651" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="C651" s="1" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A652" s="1">
-        <v>42657</v>
-      </c>
-      <c r="B652" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="C652" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A653" s="1">
-        <v>42670</v>
-      </c>
-      <c r="B653" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C653" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A654" s="1">
-        <v>42671</v>
-      </c>
-      <c r="B654" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="C654" s="1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A655" s="1">
-        <v>42704</v>
-      </c>
-      <c r="B655" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="C655" s="1" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A656" s="1">
-        <v>42712</v>
-      </c>
-      <c r="B656" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="C656" s="1" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A657" s="1">
-        <v>42753</v>
-      </c>
-      <c r="B657" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="C657" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A658" s="1">
-        <v>42777</v>
-      </c>
-      <c r="B658" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="C658" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A659" s="1">
-        <v>42817</v>
-      </c>
-      <c r="B659" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="C659" s="1" t="s">
-        <v>663</v>
       </c>
     </row>
   </sheetData>
